--- a/artfynd/A 31828-2023 artfynd.xlsx
+++ b/artfynd/A 31828-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31828-2023 artfynd.xlsx
+++ b/artfynd/A 31828-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107053742</v>
+        <v>113007343</v>
       </c>
       <c r="B2" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mossen, Srm</t>
+          <t>Segersäng, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668293.0665894807</v>
+        <v>668232</v>
       </c>
       <c r="R2" t="n">
-        <v>6547548.826838649</v>
+        <v>6547420</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,18 +757,339 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>klen björklåga</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>107053738</v>
+      </c>
+      <c r="B3" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>mossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>668306</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6547563</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Greensway AB</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Adam Trapp</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>NVI Segersäng (Norconsult AB för Trafikverket, 2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>107053742</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>mossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>668293</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6547549</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Adam Trapp</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>NVI Segersäng (Norconsult AB för Trafikverket, 2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107053743</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Segersängstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>668216</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6547428</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Adam Trapp</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>NVI Segersäng (Norconsult AB för Trafikverket, 2022)</t>
         </is>
